--- a/students/Джаббаров Неймадди Али оглы/laba3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
+++ b/students/Джаббаров Неймадди Али оглы/laba3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neyma\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neyma\Desktop\OOOOO\students\Джаббаров Неймадди Али оглы\laba3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A223E9D2-AB32-4F09-9A40-0E3CA90E41C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704DFAD4-E69C-4580-98CE-A198CB626BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -325,9 +325,6 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>6.5</t>
-  </si>
-  <si>
     <t>Аутентификация и роли</t>
   </si>
   <si>
@@ -457,7 +454,22 @@
     <t xml:space="preserve">	Прототипирование интерфейса</t>
   </si>
   <si>
-    <t>Отчетность</t>
+    <t xml:space="preserve">6.4.1 </t>
+  </si>
+  <si>
+    <t>Сбор и анализ требований заказчика</t>
+  </si>
+  <si>
+    <t>Описание функциональных требований</t>
+  </si>
+  <si>
+    <t>Описание нефункциональных требований</t>
+  </si>
+  <si>
+    <t>6.4.2</t>
+  </si>
+  <si>
+    <t>6.4.3</t>
   </si>
 </sst>
 </file>
@@ -1301,6 +1313,72 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1312,72 +1390,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1698,9 +1710,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68"/>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
+      <c r="A1" s="90"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="37" t="s">
@@ -1714,93 +1726,93 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
       <c r="D2" s="38"/>
       <c r="E2" s="36" t="s">
         <v>43</v>
       </c>
       <c r="F2" s="3">
         <f>E71</f>
-        <v>184</v>
+        <v>276</v>
       </c>
       <c r="G2" s="3">
         <f>G71</f>
-        <v>822</v>
+        <v>1068</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="70" t="s">
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="70"/>
+      <c r="E3" s="92"/>
       <c r="F3" s="3">
         <f>F2/8</f>
-        <v>23</v>
+        <v>34.5</v>
       </c>
       <c r="G3" s="3">
         <f>G2/8</f>
-        <v>102.75</v>
+        <v>133.5</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="70" t="s">
+      <c r="A4" s="90"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="70"/>
+      <c r="E4" s="92"/>
       <c r="F4" s="3">
         <f>F3/22</f>
-        <v>1.0454545454545454</v>
+        <v>1.5681818181818181</v>
       </c>
       <c r="G4" s="3">
         <f>G3/22</f>
-        <v>4.6704545454545459</v>
+        <v>6.0681818181818183</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="68"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="70" t="s">
+      <c r="A5" s="90"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="70"/>
+      <c r="E5" s="92"/>
       <c r="F5" s="3">
         <f>F4/2</f>
-        <v>0.52272727272727271</v>
+        <v>0.78409090909090906</v>
       </c>
       <c r="G5" s="3">
         <f>G4/2</f>
-        <v>2.3352272727272729</v>
+        <v>3.0340909090909092</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="69"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="70" t="s">
+      <c r="A6" s="91"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="70"/>
+      <c r="E6" s="92"/>
       <c r="F6" s="4">
         <v>300</v>
       </c>
@@ -1812,17 +1824,17 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="71"/>
+      <c r="E7" s="93"/>
       <c r="F7" s="5">
         <f>F6*H71</f>
-        <v>112899.99999999997</v>
+        <v>201600</v>
       </c>
       <c r="G7" s="5">
         <f>G6*H71</f>
-        <v>131716.66666666663</v>
+        <v>235200</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -1879,7 +1891,7 @@
         <v>50</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
@@ -1895,20 +1907,20 @@
         <v>14</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" s="50">
         <v>4</v>
       </c>
       <c r="F11" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" s="52">
         <v>12</v>
       </c>
       <c r="H11" s="42">
         <f>(E11 + 4*F11 + G11)/6</f>
-        <v>6.666666666666667</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -1920,20 +1932,20 @@
         <v>15</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="50">
         <v>2</v>
       </c>
       <c r="F12" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="52">
         <v>8</v>
       </c>
       <c r="H12" s="42">
         <f>(E12 + 4*F12 + G12)/6</f>
-        <v>3.6666666666666665</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="J12" s="2"/>
     </row>
@@ -1944,20 +1956,20 @@
         <v>16</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" s="50">
         <v>3</v>
       </c>
       <c r="F13" s="51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="52">
         <v>10</v>
       </c>
       <c r="H13" s="42">
         <f t="shared" ref="H13:H61" si="0">(E13 + 4*F13 + G13)/6</f>
-        <v>5.5</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="J13" s="2"/>
     </row>
@@ -1968,20 +1980,20 @@
         <v>17</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" s="50">
         <v>2</v>
       </c>
       <c r="F14" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G14" s="52">
         <v>10</v>
       </c>
       <c r="H14" s="42">
         <f>(E14 + 4*F14 + G14)/6</f>
-        <v>4.666666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="J14" s="2"/>
     </row>
@@ -1992,20 +2004,20 @@
         <v>18</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="50">
         <v>3</v>
       </c>
       <c r="F15" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G15" s="52">
         <v>16</v>
       </c>
       <c r="H15" s="42">
         <f>(E15 + 4*F15 + G15)/6</f>
-        <v>7.166666666666667</v>
+        <v>9.1666666666666661</v>
       </c>
       <c r="J15" s="2"/>
     </row>
@@ -2018,7 +2030,7 @@
         <v>51</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
@@ -2033,20 +2045,20 @@
         <v>19</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E17" s="50">
         <v>8</v>
       </c>
       <c r="F17" s="51">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G17" s="52">
         <v>36</v>
       </c>
       <c r="H17" s="42">
         <f>(E17 + 4*F17 + G17)/6</f>
-        <v>16.666666666666668</v>
+        <v>20</v>
       </c>
       <c r="J17" s="2"/>
     </row>
@@ -2057,20 +2069,20 @@
         <v>20</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E18" s="50">
         <v>6</v>
       </c>
       <c r="F18" s="51">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G18" s="52">
         <v>27</v>
       </c>
       <c r="H18" s="42">
         <f>(E18 + 4*F18 + G18)/6</f>
-        <v>12.166666666666666</v>
+        <v>16.166666666666668</v>
       </c>
       <c r="J18" s="2"/>
     </row>
@@ -2081,20 +2093,20 @@
         <v>21</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" s="50">
         <v>4</v>
       </c>
       <c r="F19" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G19" s="52">
         <v>18</v>
       </c>
       <c r="H19" s="42">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="J19" s="2"/>
     </row>
@@ -2105,20 +2117,20 @@
         <v>22</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E20" s="50">
         <v>4</v>
       </c>
       <c r="F20" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="52">
         <v>20</v>
       </c>
       <c r="H20" s="42">
         <f t="shared" si="0"/>
-        <v>9.3333333333333339</v>
+        <v>8</v>
       </c>
       <c r="J20" s="2"/>
     </row>
@@ -2129,7 +2141,7 @@
         <v>52</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21" s="56"/>
       <c r="F21" s="56"/>
@@ -2144,20 +2156,20 @@
         <v>23</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="50">
         <v>10</v>
       </c>
       <c r="F22" s="51">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G22" s="52">
         <v>42</v>
       </c>
       <c r="H22" s="42">
         <f t="shared" si="0"/>
-        <v>19.333333333333332</v>
+        <v>22</v>
       </c>
       <c r="J22" s="2"/>
     </row>
@@ -2168,20 +2180,20 @@
         <v>24</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E23" s="50">
         <v>12</v>
       </c>
       <c r="F23" s="51">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G23" s="52">
         <v>54</v>
       </c>
       <c r="H23" s="42">
         <f t="shared" si="0"/>
-        <v>24.333333333333332</v>
+        <v>27.666666666666668</v>
       </c>
       <c r="J23" s="2"/>
     </row>
@@ -2192,20 +2204,20 @@
         <v>25</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E24" s="50">
         <v>6</v>
       </c>
       <c r="F24" s="51">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G24" s="52">
         <v>27</v>
       </c>
       <c r="H24" s="42">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>15.5</v>
       </c>
       <c r="J24" s="2"/>
     </row>
@@ -2216,7 +2228,7 @@
         <v>53</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E25" s="56"/>
       <c r="F25" s="56"/>
@@ -2231,20 +2243,20 @@
         <v>26</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26" s="50">
         <v>6</v>
       </c>
       <c r="F26" s="51">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G26" s="52">
         <v>27</v>
       </c>
       <c r="H26" s="42">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>15.5</v>
       </c>
       <c r="J26" s="2"/>
     </row>
@@ -2255,20 +2267,20 @@
         <v>27</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E27" s="50">
         <v>5</v>
       </c>
       <c r="F27" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G27" s="52">
         <v>22</v>
       </c>
       <c r="H27" s="42">
         <f t="shared" si="0"/>
-        <v>9.8333333333333339</v>
+        <v>10.5</v>
       </c>
       <c r="J27" s="2"/>
     </row>
@@ -2279,20 +2291,20 @@
         <v>28</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E28" s="50">
         <v>3</v>
       </c>
       <c r="F28" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G28" s="52">
         <v>14</v>
       </c>
       <c r="H28" s="42">
         <f t="shared" si="0"/>
-        <v>6.166666666666667</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="J28" s="2"/>
     </row>
@@ -2303,7 +2315,7 @@
         <v>54</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E29" s="56"/>
       <c r="F29" s="56"/>
@@ -2318,20 +2330,20 @@
         <v>29</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E30" s="57">
         <v>8</v>
       </c>
       <c r="F30" s="58">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G30" s="59">
         <v>36</v>
       </c>
       <c r="H30" s="42">
         <f t="shared" si="0"/>
-        <v>16.666666666666668</v>
+        <v>20</v>
       </c>
       <c r="J30" s="2"/>
     </row>
@@ -2342,7 +2354,7 @@
         <v>55</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E31" s="56"/>
       <c r="F31" s="56"/>
@@ -2357,20 +2369,20 @@
         <v>30</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E32" s="60">
         <v>4</v>
       </c>
       <c r="F32" s="61">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" s="59">
         <v>18</v>
       </c>
       <c r="H32" s="42">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>9</v>
       </c>
       <c r="J32" s="2"/>
     </row>
@@ -2381,7 +2393,7 @@
         <v>31</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E33" s="57">
         <v>3</v>
@@ -2405,7 +2417,7 @@
         <v>56</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E34" s="56"/>
       <c r="F34" s="56"/>
@@ -2420,83 +2432,83 @@
         <v>32</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E35" s="57">
         <v>4</v>
       </c>
       <c r="F35" s="58">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G35" s="59">
         <v>18</v>
       </c>
       <c r="H35" s="42">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="J35" s="2"/>
     </row>
     <row r="36" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="84"/>
-      <c r="B36" s="84"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="80"/>
       <c r="C36" s="24" t="s">
         <v>42</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E36" s="60">
         <v>4</v>
       </c>
       <c r="F36" s="61">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G36" s="67">
         <v>18</v>
       </c>
       <c r="H36" s="42">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="J36" s="2"/>
     </row>
     <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="85"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="73"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="75"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="86"/>
+      <c r="A37" s="81"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="82"/>
       <c r="H37" s="42"/>
       <c r="J37" s="2"/>
     </row>
     <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="87"/>
-      <c r="B38" s="88"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="91"/>
-      <c r="F38" s="92"/>
-      <c r="G38" s="93"/>
+      <c r="A38" s="83"/>
+      <c r="B38" s="84"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="86"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="88"/>
+      <c r="G38" s="89"/>
       <c r="H38" s="42"/>
       <c r="J38" s="2"/>
     </row>
     <row r="39" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="77"/>
-      <c r="B39" s="78">
+      <c r="A39" s="73"/>
+      <c r="B39" s="74">
         <v>2</v>
       </c>
-      <c r="C39" s="79" t="s">
+      <c r="C39" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="80" t="s">
+      <c r="D39" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="E39" s="81"/>
-      <c r="F39" s="82"/>
-      <c r="G39" s="83"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="79"/>
       <c r="H39" s="42"/>
       <c r="J39" s="2"/>
     </row>
@@ -2507,20 +2519,20 @@
         <v>57</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E40" s="57">
         <v>6</v>
       </c>
       <c r="F40" s="58">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G40" s="59">
         <v>27</v>
       </c>
       <c r="H40" s="42">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>17.5</v>
       </c>
       <c r="J40" s="2"/>
     </row>
@@ -2537,14 +2549,14 @@
         <v>5</v>
       </c>
       <c r="F41" s="58">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G41" s="59">
         <v>22</v>
       </c>
       <c r="H41" s="42">
         <f t="shared" si="0"/>
-        <v>9.8333333333333339</v>
+        <v>15.166666666666666</v>
       </c>
       <c r="J41" s="2"/>
     </row>
@@ -2561,14 +2573,14 @@
         <v>4</v>
       </c>
       <c r="F42" s="58">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G42" s="59">
         <v>18</v>
       </c>
       <c r="H42" s="42">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="J42" s="2"/>
     </row>
@@ -2585,14 +2597,14 @@
         <v>4</v>
       </c>
       <c r="F43" s="58">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G43" s="59">
         <v>18</v>
       </c>
       <c r="H43" s="42">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="J43" s="2"/>
     </row>
@@ -2609,14 +2621,14 @@
         <v>2</v>
       </c>
       <c r="F44" s="58">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G44" s="59">
         <v>9</v>
       </c>
       <c r="H44" s="42">
         <f t="shared" si="0"/>
-        <v>3.8333333333333335</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="J44" s="2"/>
     </row>
@@ -2653,20 +2665,20 @@
         <v>62</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E47" s="57">
         <v>5</v>
       </c>
       <c r="F47" s="58">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G47" s="59">
         <v>22</v>
       </c>
       <c r="H47" s="42">
         <f t="shared" si="0"/>
-        <v>9.8333333333333339</v>
+        <v>12.5</v>
       </c>
       <c r="J47" s="2"/>
     </row>
@@ -2677,20 +2689,20 @@
         <v>63</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E48" s="57">
         <v>4</v>
       </c>
       <c r="F48" s="58">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G48" s="59">
         <v>18</v>
       </c>
       <c r="H48" s="42">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>11</v>
       </c>
       <c r="J48" s="2"/>
     </row>
@@ -2707,14 +2719,14 @@
         <v>4</v>
       </c>
       <c r="F49" s="58">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G49" s="59">
         <v>18</v>
       </c>
       <c r="H49" s="42">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>16.333333333333332</v>
       </c>
       <c r="J49" s="2"/>
     </row>
@@ -2725,20 +2737,20 @@
         <v>65</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E50" s="57">
         <v>2</v>
       </c>
       <c r="F50" s="58">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G50" s="59">
         <v>9</v>
       </c>
       <c r="H50" s="42">
         <f t="shared" si="0"/>
-        <v>3.8333333333333335</v>
+        <v>9.8333333333333339</v>
       </c>
       <c r="J50" s="2"/>
     </row>
@@ -2760,7 +2772,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E52" s="63"/>
       <c r="F52" s="64"/>
@@ -2775,20 +2787,20 @@
         <v>66</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E53" s="57">
         <v>2</v>
       </c>
       <c r="F53" s="58">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G53" s="66">
         <v>10</v>
       </c>
       <c r="H53" s="42">
         <f t="shared" si="0"/>
-        <v>4.666666666666667</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="J53" s="2"/>
     </row>
@@ -2799,20 +2811,20 @@
         <v>67</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E54" s="57">
         <v>5</v>
       </c>
       <c r="F54" s="58">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G54" s="66">
         <v>22</v>
       </c>
       <c r="H54" s="42">
         <f t="shared" si="0"/>
-        <v>9.8333333333333339</v>
+        <v>16.5</v>
       </c>
       <c r="J54" s="2"/>
     </row>
@@ -2823,20 +2835,20 @@
         <v>68</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E55" s="57">
         <v>3</v>
       </c>
       <c r="F55" s="58">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G55" s="66">
         <v>14</v>
       </c>
       <c r="H55" s="42">
         <f t="shared" si="0"/>
-        <v>6.166666666666667</v>
+        <v>13.5</v>
       </c>
       <c r="J55" s="2"/>
     </row>
@@ -2873,20 +2885,20 @@
         <v>69</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E58" s="57">
         <v>8</v>
       </c>
       <c r="F58" s="58">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G58" s="59">
         <v>36</v>
       </c>
       <c r="H58" s="42">
         <f t="shared" si="0"/>
-        <v>16.666666666666668</v>
+        <v>20</v>
       </c>
       <c r="J58" s="2"/>
     </row>
@@ -2897,20 +2909,20 @@
         <v>70</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E59" s="57">
         <v>4</v>
       </c>
       <c r="F59" s="58">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G59" s="59">
         <v>18</v>
       </c>
       <c r="H59" s="42">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="J59" s="2"/>
     </row>
@@ -2921,20 +2933,20 @@
         <v>71</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E60" s="60">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="F60" s="61">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G60" s="67">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="H60" s="42">
         <f t="shared" si="0"/>
-        <v>6.166666666666667</v>
+        <v>93.333333333333329</v>
       </c>
       <c r="J60" s="2"/>
     </row>
@@ -2945,20 +2957,20 @@
         <v>72</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E61" s="57">
         <v>2</v>
       </c>
       <c r="F61" s="58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G61" s="59">
         <v>10</v>
       </c>
       <c r="H61" s="42">
         <f t="shared" si="0"/>
-        <v>4.666666666666667</v>
+        <v>6</v>
       </c>
       <c r="J61" s="2"/>
     </row>
@@ -2995,20 +3007,20 @@
         <v>73</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E64" s="57">
         <v>4</v>
       </c>
       <c r="F64" s="58">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G64" s="59">
         <v>18</v>
       </c>
       <c r="H64" s="42">
-        <f t="shared" ref="H64:H68" si="1">(E64 + 4*F64 + G64)/6</f>
-        <v>8.3333333333333339</v>
+        <f t="shared" ref="H64:H69" si="1">(E64 + 4*F64 + G64)/6</f>
+        <v>11.666666666666666</v>
       </c>
       <c r="J64" s="2"/>
     </row>
@@ -3019,20 +3031,20 @@
         <v>74</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E65" s="57">
         <v>5</v>
       </c>
       <c r="F65" s="58">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G65" s="59">
         <v>22</v>
       </c>
       <c r="H65" s="42">
         <f t="shared" si="1"/>
-        <v>9.8333333333333339</v>
+        <v>10.5</v>
       </c>
       <c r="J65" s="2"/>
     </row>
@@ -3043,20 +3055,20 @@
         <v>75</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E66" s="57">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F66" s="58">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="G66" s="59">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="H66" s="42">
         <f t="shared" si="1"/>
-        <v>12.166666666666666</v>
+        <v>92</v>
       </c>
       <c r="J66" s="2"/>
     </row>
@@ -3067,20 +3079,20 @@
         <v>76</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E67" s="57">
         <v>4</v>
       </c>
       <c r="F67" s="58">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G67" s="59">
         <v>18</v>
       </c>
       <c r="H67" s="42">
         <f t="shared" si="1"/>
-        <v>8.3333333333333339</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="J67" s="2"/>
     </row>
@@ -3088,38 +3100,69 @@
       <c r="A68" s="16"/>
       <c r="B68" s="16"/>
       <c r="C68" s="45" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>121</v>
       </c>
       <c r="E68" s="57">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F68" s="58">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G68" s="59">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H68" s="42">
         <f t="shared" si="1"/>
-        <v>2.3333333333333335</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="J68" s="2"/>
     </row>
     <row r="69" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="30"/>
       <c r="B69" s="30"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="62"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="42"/>
+      <c r="C69" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E69" s="57">
+        <v>8</v>
+      </c>
+      <c r="F69" s="62">
+        <v>14</v>
+      </c>
+      <c r="G69" s="59">
+        <v>28</v>
+      </c>
+      <c r="H69" s="42">
+        <f t="shared" si="1"/>
+        <v>15.333333333333334</v>
+      </c>
       <c r="J69" s="2"/>
     </row>
-    <row r="70" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="30"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="D70" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="E70" s="57">
+        <v>12</v>
+      </c>
+      <c r="F70" s="62">
+        <v>7</v>
+      </c>
+      <c r="G70" s="59">
+        <v>18</v>
+      </c>
+    </row>
     <row r="71" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="34" t="s">
         <v>36</v>
@@ -3128,20 +3171,20 @@
       <c r="C71" s="31"/>
       <c r="D71" s="27"/>
       <c r="E71" s="35">
-        <f>SUM(E6:E69)</f>
-        <v>184</v>
+        <f>SUM(E6:E70)</f>
+        <v>276</v>
       </c>
       <c r="F71" s="35">
-        <f>SUM(F11:F69)</f>
-        <v>313</v>
+        <f>SUM(F11:F68)</f>
+        <v>661</v>
       </c>
       <c r="G71" s="35">
         <f>SUM(G11:G69)</f>
-        <v>822</v>
+        <v>1068</v>
       </c>
       <c r="H71" s="35">
         <f>SUM(H6:H69)</f>
-        <v>376.33333333333326</v>
+        <v>672</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
